--- a/uploads/INV101 - Introduccion a la Investigacion-REV/bases_de_datos/CONTROL_VERSIONES_DOCUMENTAL.xlsx
+++ b/uploads/INV101 - Introduccion a la Investigacion-REV/bases_de_datos/CONTROL_VERSIONES_DOCUMENTAL.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -556,7 +556,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Registro Oficial de Versiones Vigentes y Trazabilidad de Evidencias Curriculares • Emisión: 06/09/2026 20:55</t>
+          <t>Registro Oficial de Versiones Vigentes y Trazabilidad de Evidencias Curriculares • Emisión: 06/09/2026 21:12</t>
         </is>
       </c>
     </row>
@@ -610,45 +610,233 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
+          <t>DOC-CP2-VER-INV101</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Libro Oficial de Control de Versiones y Trazabilidad Curricular</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Registro Maestro de Control de Versiones</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>06/09/2026 21:12</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Sistema de Gestión de Calidad (ISO 21001)</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Edición Manual Docente</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>f3e3466ab29c4302...</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>Aprobado Institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>DOC-CP2-BASE-INV101</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Base de Datos Integrada y Curada</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Base de Datos de Aula Consolidada</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>06/09/2026 21:12</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Agente Etapa 1 (Ingesta &amp; Fusión)</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Pipeline IA Autónomo</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>50b46ef40d39f0a7...</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>Aprobado Institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>DOC-DIR-CP2-DOSSIER-INV101In</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>CARPETA_PEDAGOGICA_CONSOLIDADA_INV101_-_Introduccion_a_la_Investigacion.docx</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Dossier Oficial Consolidado (Auditoría)</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>06/09/2026 21:12</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Servicio Dossier Institucional (CP2)</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Edición Manual Docente</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>c39eab113af2049e...</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>Aprobado Institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>DOC-DIR-CP2-DUA-INV101In</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>MATRIZ_ADAPTACIONES_DUA_INV101_-_Introduccion_a_la_Investigacion.docx</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Matriz de Ajustes Razonables (Inclusión DUA)</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>06/09/2026 21:12</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Servicio DUA Institucional</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Edición Manual Docente</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>530e58432f308119...</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>Aprobado Institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
           <t>DOC-DIR-CP2-PDC-INV101</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Plan de Aprendizaje Modular CBL - INV101 - Introduccion a la Investigacion</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Planificación Didáctica Modular</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>06/09/2026 20:55</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>06/09/2026 21:12</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Motor de Planificación CBL / UbD</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Edición Manual Docente</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>c30da2962c7d680a...</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>988dd75d787f64ab...</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Aprobado Institucional</t>
         </is>
@@ -670,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -741,30 +929,178 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>06/09/2026 20:55</t>
+          <t>06/09/2026 21:12</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
+          <t>Libro Oficial de Control de Versiones y Trazabilidad Curricular</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>0.0 -&gt; 1.0</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Sistema de Gestión de Calidad (ISO 21001)</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Inicialización de la matriz de versiones y bitácora inmutable de auditoría.</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Aseguramiento de la información documentada (ISO 21001:2018 Cláusula 7.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>EVT-002</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>06/09/2026 21:12</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Base de Datos Integrada y Curada</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>0.0 -&gt; 1.0</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Agente Etapa 1 (Ingesta &amp; Fusión)</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Consolidación de planillas de asistencia, notas y evidencias en libro maestro.</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Estandarización de datos de rendimiento académico para analítica de aprendizaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>EVT-003</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>06/09/2026 21:12</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>CARPETA_PEDAGOGICA_CONSOLIDADA_INV101_-_Introduccion_a_la_Investigacion.docx</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>0.0 -&gt; 1.0</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Servicio Dossier Institucional (CP2)</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Compilación consolidada de Portada ISO, Caracterización, Diagnóstico Analítico, Plan Modular, Evaluación 100% y Matriz DUA.</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Aseguramiento de calidad académica según estándar ISO 21001 Cláusula 7.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>EVT-004</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>06/09/2026 21:12</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>MATRIZ_ADAPTACIONES_DUA_INV101_-_Introduccion_a_la_Investigacion.docx</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>0.0 -&gt; 1.0</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Servicio DUA Institucional</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Alineación curricular DUA (CAST 2024) para 25 estudiantes.</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Cumplimiento de equidad, inclusión educativa y principio de no discriminación (ISO 21001).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>EVT-005</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>06/09/2026 21:12</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
           <t>Plan de Aprendizaje Modular CBL - INV101 - Introduccion a la Investigacion</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>0.0 -&gt; 1.0</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Motor de Planificación CBL / UbD</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Compilación oficial del Plan de Aprendizaje Modular con alineamiento constructivo, créditos SCT e inclusión DUA.</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Aseguramiento del diseño curricular modular bajo estándar ISO 21001:2018 Cláusula 7.5.</t>
         </is>
